--- a/output/pdf_financials_xlsx/EAU.xlsx
+++ b/output/pdf_financials_xlsx/EAU.xlsx
@@ -3078,25 +3078,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.098167</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.269052</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.8192199999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.835716</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.836836</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.836836</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.836836</v>
       </c>
     </row>
     <row r="93">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.197934</v>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
@@ -3831,19 +3831,19 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.12</v>
+        <v>-0.346894</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.200651</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>0.022778</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.013082</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000627</v>
       </c>
     </row>
     <row r="119">
@@ -5226,7 +5226,11 @@
           <t>Share-based payment reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -5516,7 +5520,11 @@
           <t>Share-based payment reserves (Notes 7 and 8)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -5914,7 +5922,11 @@
           <t>Reserves (Notes 7 and 8)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -6263,7 +6275,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.098167</v>
       </c>
@@ -6992,7 +7008,11 @@
           <t>Exploration and evaluation asset expenditures, net</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -8594,7 +8614,11 @@
           <t>Exploration and evaluation asset expenditures (916,906)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>-0.197934</v>
       </c>
@@ -9495,7 +9519,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="n">
         <v>-0.197934</v>
       </c>

--- a/output/pdf_financials_xlsx/EAU.xlsx
+++ b/output/pdf_financials_xlsx/EAU.xlsx
@@ -1422,25 +1422,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.08499900000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000735</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.554346</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.107522</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001514</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001449</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
     </row>
     <row r="35">
@@ -1478,25 +1478,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.08499900000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000735</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.554346</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.107522</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001514</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001449</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
     </row>
     <row r="37">
@@ -1814,25 +1814,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.094584</v>
+        <v>0.009585</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.003735</v>
+        <v>0.003</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.5784629999999999</v>
+        <v>0.024117</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.140881</v>
+        <v>0.033359</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.012491</v>
+        <v>0.010977</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.013158</v>
+        <v>0.011709</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.019552</v>
+        <v>0.01955</v>
       </c>
     </row>
     <row r="49">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
